--- a/healthcare_assessment_forms/016_kinetic_chain_assessment_form--healthcare_assessment_forms.xlsx
+++ b/healthcare_assessment_forms/016_kinetic_chain_assessment_form--healthcare_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Client Info</t>
+          <t>Client Information</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -869,12 +869,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -915,177 +915,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Select One</t>
+          <t>Select One 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Select Multiple</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,11 +941,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -1135,12 +974,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1152,12 +991,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1008,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1025,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1042,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1220,114 +1059,63 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
